--- a/林靖凯爬虫自查结果.xlsx
+++ b/林靖凯爬虫自查结果.xlsx
@@ -2480,76 +2480,76 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>林靖凯</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="25" t="n">
         <v>3134</v>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>《绢画幡带》</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="27" t="inlineStr">
         <is>
           <t>https://www.sinoss.net/uploadfile/2010/1130/10620.pdf</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="G29" s="27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="inlineStr">
         <is>
           <t>宁夏博物馆 王效军《宁夏博物馆藏西夏文献概述》，《西夏学》第1辑，2006年10月，页150-153</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>贺兰县宏佛塔天宫出土西夏绢质幡带（宁夏博物馆藏）</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J29" s="28" t="inlineStr">
         <is>
           <t>找到</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>正确</t>
-        </is>
-      </c>
-      <c r="L29" s="18" t="inlineStr">
+      <c r="K29" s="28" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
+      <c r="L29" s="29" t="inlineStr">
         <is>
           <t>马雨衡</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr">
+      <c r="M29" s="28" t="inlineStr">
         <is>
           <t>含绢画幡带的具体内容描述。</t>
         </is>
       </c>
-      <c r="N29" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O29" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P29" s="9" t="inlineStr">
+      <c r="N29" s="28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O29" s="28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P29" s="28" t="inlineStr">
         <is>
           <t>林靖凯\爬取结果\3134绢画幡带\宏佛塔出土绢质幡带.txt</t>
         </is>
@@ -2751,76 +2751,76 @@
       <c r="L32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>林靖凯</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="25" t="n">
         <v>3646</v>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>《修正待遇蒙藏学生章程》</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="27" t="inlineStr">
         <is>
           <t>https://jykxxy.nwnu.edu.cn/_upload/article/files/d1/ba/913455664c90b1378932096c74e9/4ec8680b-334e-4216-8a46-aaede14fb109.pdf</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>不详</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>不详</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="G33" s="27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="inlineStr">
+        <is>
+          <t>不详</t>
+        </is>
+      </c>
+      <c r="I33" s="27" t="inlineStr">
+        <is>
+          <t>不详</t>
+        </is>
+      </c>
+      <c r="J33" s="28" t="inlineStr">
         <is>
           <t>找到</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>正确</t>
-        </is>
-      </c>
-      <c r="L33" s="18" t="inlineStr">
+      <c r="K33" s="28" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
+      <c r="L33" s="29" t="inlineStr">
         <is>
           <t>马雨衡</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="M33" s="28" t="inlineStr">
         <is>
           <t>条目与本地资料对应；研究文章直接引录章程待遇、入学等条款，计正文节录。</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O33" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P33" s="9" t="inlineStr">
+      <c r="N33" s="28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O33" s="28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P33" s="28" t="inlineStr">
         <is>
           <t>林靖凯\爬取结果\3646修正待遇蒙藏学生章程\本轮补充\匹配资料_93af3c489ed7ffe9.txt</t>
         </is>
@@ -3566,76 +3566,76 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="23" t="inlineStr">
+      <c r="A46" s="24" t="inlineStr">
         <is>
           <t>林靖凯</t>
         </is>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="25" t="n">
         <v>5317</v>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="26" t="inlineStr">
         <is>
           <t>《安徽合肥大雁墩遗址发掘简报》</t>
         </is>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="27" t="inlineStr">
         <is>
           <t>https://m.fx361.com/news/2022/0706/11289877.html https://journal.yuanpingjia.com.cn/Journal/ArticleDetails/37633 http://www.ncha.gov.cn/art/2022/5/24/art_2600_174489.html http://www.silkroads.org.cn/portal.php?aid=86602&amp;mod=view https://zh.wikipedia.org/wiki/大雁墩古文化遗址</t>
         </is>
       </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="G46" s="27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="inlineStr">
         <is>
           <t>《东南文化》（安徽大学历史学院、安徽省文物考古研究所）</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>2022年第3期，第44—55页，中插3</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr">
+      <c r="J46" s="28" t="inlineStr">
         <is>
           <t>找到</t>
         </is>
       </c>
-      <c r="K46" s="9" t="inlineStr">
-        <is>
-          <t>正确</t>
-        </is>
-      </c>
-      <c r="L46" s="18" t="inlineStr">
+      <c r="K46" s="28" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
+      <c r="L46" s="29" t="inlineStr">
         <is>
           <t>韦广波</t>
         </is>
       </c>
-      <c r="M46" s="9" t="inlineStr">
+      <c r="M46" s="28" t="inlineStr">
         <is>
           <t>有发掘简报开头正文，属节录。</t>
         </is>
       </c>
-      <c r="N46" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O46" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P46" s="9" t="inlineStr">
+      <c r="N46" s="28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O46" s="28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P46" s="28" t="inlineStr">
         <is>
           <t>林靖凯\爬取结果\5317安徽合肥大雁墩遗址发掘简报\安徽合肥大雁墩遗址发掘简报（节选）.txt</t>
         </is>
@@ -4000,76 +4000,76 @@
       <c r="L53" s="17" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="23" t="inlineStr">
+      <c r="A54" s="24" t="inlineStr">
         <is>
           <t>林靖凯</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="25" t="n">
         <v>6341</v>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="26" t="inlineStr">
         <is>
           <t>《中国工农红军四方面军总政治部关于宣传教育工作决议草案（摘录）》</t>
         </is>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="D54" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E54" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F54" s="27" t="inlineStr">
         <is>
           <t>https://epaper.neamco.com/gmrb/html/2019-12/11/nw.D110000gmrb_20191211_2-11.htm</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="G54" s="27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H54" s="27" t="inlineStr">
         <is>
           <t>光明日报（张燚、黎海波《长征时期中国共产党民族政策宣传的历史经验》）</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>2019年12月11日11版；引《民族问题文献汇编》中共中央党校出版社1991年版第401页</t>
         </is>
       </c>
-      <c r="J54" s="9" t="inlineStr">
+      <c r="J54" s="28" t="inlineStr">
         <is>
           <t>找到</t>
         </is>
       </c>
-      <c r="K54" s="9" t="inlineStr">
-        <is>
-          <t>正确</t>
-        </is>
-      </c>
-      <c r="L54" s="18" t="inlineStr">
+      <c r="K54" s="28" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
+      <c r="L54" s="29" t="inlineStr">
         <is>
           <t>马雨衡</t>
         </is>
       </c>
-      <c r="M54" s="9" t="inlineStr">
+      <c r="M54" s="28" t="inlineStr">
         <is>
           <t>有决议草案原文摘录。</t>
         </is>
       </c>
-      <c r="N54" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O54" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P54" s="9" t="inlineStr">
+      <c r="N54" s="28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O54" s="28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P54" s="28" t="inlineStr">
         <is>
           <t>林靖凯\爬取结果\6341中国工农红军四方面军总政治部关于宣传教育工作决议草案（摘录）\关于宣传教育工作决议草案（摘录）.txt</t>
         </is>
@@ -5562,76 +5562,76 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="23" t="inlineStr">
+      <c r="A80" s="24" t="inlineStr">
         <is>
           <t>林靖凯</t>
         </is>
       </c>
-      <c r="B80" s="6" t="n">
+      <c r="B80" s="25" t="n">
         <v>9672</v>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C80" s="26" t="inlineStr">
         <is>
           <t>《镶银扣绿玻璃方盘》</t>
         </is>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="D80" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E80" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F80" s="10" t="inlineStr">
+      <c r="F80" s="27" t="inlineStr">
         <is>
           <t>https://www.sohu.com/a/398869833_120065441</t>
         </is>
       </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>不详</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>不详</t>
-        </is>
-      </c>
-      <c r="J80" s="9" t="inlineStr">
+      <c r="G80" s="27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H80" s="27" t="inlineStr">
+        <is>
+          <t>不详</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>不详</t>
+        </is>
+      </c>
+      <c r="J80" s="28" t="inlineStr">
         <is>
           <t>找到</t>
         </is>
       </c>
-      <c r="K80" s="9" t="inlineStr">
-        <is>
-          <t>正确</t>
-        </is>
-      </c>
-      <c r="L80" s="18" t="inlineStr">
+      <c r="K80" s="28" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
+      <c r="L80" s="29" t="inlineStr">
         <is>
           <t>马雨衡</t>
         </is>
       </c>
-      <c r="M80" s="9" t="inlineStr">
+      <c r="M80" s="28" t="inlineStr">
         <is>
           <t>有目标文物的具体内容讲解。</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="O80" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P80" s="9" t="inlineStr">
+      <c r="N80" s="28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="O80" s="28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P80" s="28" t="inlineStr">
         <is>
           <t>林靖凯\爬取结果\9672镶银扣绿玻璃方盘\本轮补充\匹配资料_0eaff4e0da405d0d.txt</t>
         </is>
